--- a/Consolidated_Book_of_Negroes_v11_subset.xlsx
+++ b/Consolidated_Book_of_Negroes_v11_subset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\North_American_Management_Work\compare_book_of_negroes_records\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99239E03-5864-4FFD-A00C-BB5012034FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F73700D-007E-4A42-B199-615D05734285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="46035" yWindow="0" windowWidth="26160" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
